--- a/05. Res/modelos/coeficientes_poisson.xlsx
+++ b/05. Res/modelos/coeficientes_poisson.xlsx
@@ -466,16 +466,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.54517452368271</v>
+        <v>-1.75767420440689</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0597967761568201</v>
+        <v>0.0617626354008843</v>
       </c>
       <c r="D2" t="n">
-        <v>-25.8404319261361</v>
+        <v>-28.4585363464223</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000311685290615929</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000382107041733895</v>
       </c>
     </row>
     <row r="3">
@@ -483,16 +483,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>0.667123434716253</v>
+        <v>0.853744031750938</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0386192437149024</v>
+        <v>0.0377673951304568</v>
       </c>
       <c r="D3" t="n">
-        <v>17.2743785362846</v>
+        <v>22.6053194508629</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000733593620531926</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000038418641438973</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>0.569306441492496</v>
+        <v>0.758061857671197</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0362287583748751</v>
+        <v>0.0353007669010474</v>
       </c>
       <c r="D4" t="n">
-        <v>15.7142134323685</v>
+        <v>21.4743736246904</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000012087198501276</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000270339848818435</v>
       </c>
     </row>
     <row r="5">
@@ -517,16 +517,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>-4.13444862220598</v>
+        <v>-3.96296614019794</v>
       </c>
       <c r="C5" t="n">
-        <v>1.00073498406393</v>
+        <v>1.00072216518003</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.13141210015085</v>
+        <v>-3.96010628932659</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0000360541557658915</v>
+        <v>0.0000749164113617913</v>
       </c>
     </row>
     <row r="6">
@@ -534,16 +534,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="n">
-        <v>0.046071604076446</v>
+        <v>0.0271981818607928</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0122490932589752</v>
+        <v>0.0122034025561298</v>
       </c>
       <c r="D6" t="n">
-        <v>3.76122567625064</v>
+        <v>2.22873757836753</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000169082790243717</v>
+        <v>0.0258313703828192</v>
       </c>
     </row>
     <row r="7">
@@ -551,16 +551,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.205115787045603</v>
+        <v>0.0803617976539967</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0445247387287241</v>
+        <v>0.0462696528930763</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.60678249669946</v>
+        <v>1.73681436166602</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00000408947360966689</v>
+        <v>0.0824199432376273</v>
       </c>
     </row>
     <row r="8">
@@ -568,16 +568,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.293659861096734</v>
+        <v>-0.0118967947846802</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0458286030903412</v>
+        <v>0.0471433751486309</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.40778555955211</v>
+        <v>-0.25235348014801</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000000000147648373977562</v>
+        <v>0.800767854161033</v>
       </c>
     </row>
     <row r="9">
@@ -585,16 +585,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.155502145485465</v>
+        <v>0.0435368790390522</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0473458833588045</v>
+        <v>0.0488054592307569</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.28438576817783</v>
+        <v>0.892049367535005</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00102204920751265</v>
+        <v>0.372366472037836</v>
       </c>
     </row>
     <row r="10">
@@ -602,16 +602,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.289365582283758</v>
+        <v>-0.0935349312020425</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0486328653415811</v>
+        <v>0.0501585118438778</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.95000068886235</v>
+        <v>-1.86478680813293</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00000000268141360279761</v>
+        <v>0.0622112931182075</v>
       </c>
     </row>
     <row r="11">
@@ -619,16 +619,16 @@
         <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.436430387660355</v>
+        <v>-0.17367063233217</v>
       </c>
       <c r="C11" t="n">
-        <v>0.051645657038935</v>
+        <v>0.0528472423554447</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.45047604547533</v>
+        <v>-3.28627615352341</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0000000000000000290117437553305</v>
+        <v>0.00101521427690082</v>
       </c>
     </row>
     <row r="12">
@@ -636,16 +636,16 @@
         <v>15</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.414597592865965</v>
+        <v>-0.766375773543299</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0605460516532197</v>
+        <v>0.0626988430499868</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.84764045788801</v>
+        <v>-12.2231246425441</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00000000000750779660877638</v>
+        <v>0.000000000000000000000000000000000233917760310326</v>
       </c>
     </row>
     <row r="13">
@@ -653,16 +653,16 @@
         <v>16</v>
       </c>
       <c r="B13" t="n">
-        <v>0.034325202286913</v>
+        <v>-0.128234999239622</v>
       </c>
       <c r="C13" t="n">
-        <v>0.056136093767102</v>
+        <v>0.0571787941854216</v>
       </c>
       <c r="D13" t="n">
-        <v>0.611464032914755</v>
+        <v>-2.24270205530702</v>
       </c>
       <c r="E13" t="n">
-        <v>0.540892422449087</v>
+        <v>0.0249160340193095</v>
       </c>
     </row>
     <row r="14">
@@ -670,16 +670,16 @@
         <v>17</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.195132606414289</v>
+        <v>-0.317410775439775</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0563241283276204</v>
+        <v>0.0570883591560815</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.46445852262927</v>
+        <v>-5.55999121593183</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00053130006465526</v>
+        <v>0.000000026978822854356</v>
       </c>
     </row>
     <row r="15">
@@ -687,16 +687,16 @@
         <v>18</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.236770446639478</v>
+        <v>-0.299127714732782</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0578066566947341</v>
+        <v>0.0583702178620998</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.09590279351075</v>
+        <v>-5.12466332470223</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0000420526368032544</v>
+        <v>0.000000298069876736473</v>
       </c>
     </row>
     <row r="16">
@@ -704,16 +704,16 @@
         <v>19</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.0867297596137126</v>
+        <v>-0.130211269249286</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0167620444274117</v>
+        <v>0.0167292617043201</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.17417550044669</v>
+        <v>-7.78344385727798</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000000228919579781564</v>
+        <v>0.00000000000000705764802547613</v>
       </c>
     </row>
     <row r="17">
@@ -721,16 +721,16 @@
         <v>20</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.167277569646248</v>
+        <v>-0.108722711381466</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0179434618942731</v>
+        <v>0.0181857211153</v>
       </c>
       <c r="D17" t="n">
-        <v>-9.32248027899441</v>
+        <v>-5.97846578049607</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0000000000000000000113651865570476</v>
+        <v>0.00000000225248915502147</v>
       </c>
     </row>
     <row r="18">
@@ -738,16 +738,16 @@
         <v>21</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.153284040671566</v>
+        <v>-0.148079488131958</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0337554534629327</v>
+        <v>0.0343686843706417</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.54101559737272</v>
+        <v>-4.30855852772909</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00000559838892714387</v>
+        <v>0.0000164321995018246</v>
       </c>
     </row>
     <row r="19">
@@ -755,16 +755,16 @@
         <v>22</v>
       </c>
       <c r="B19" t="n">
-        <v>0.147132102102957</v>
+        <v>0.0799800884829761</v>
       </c>
       <c r="C19" t="n">
-        <v>0.019577347790056</v>
+        <v>0.019122148560131</v>
       </c>
       <c r="D19" t="n">
-        <v>7.51542566852136</v>
+        <v>4.18258901354484</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0000000000000567260593519306</v>
+        <v>0.0000288208118177122</v>
       </c>
     </row>
     <row r="20">
@@ -772,16 +772,16 @@
         <v>23</v>
       </c>
       <c r="B20" t="n">
-        <v>0.274487353057273</v>
+        <v>0.171498622285334</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0209458286451106</v>
+        <v>0.020802080193115</v>
       </c>
       <c r="D20" t="n">
-        <v>13.1046308889453</v>
+        <v>8.24430156471066</v>
       </c>
       <c r="E20" t="n">
-        <v>0.00000000000000000000000000000000000000309765575685599</v>
+        <v>0.000000000000000166127699825894</v>
       </c>
     </row>
     <row r="21">
@@ -789,16 +789,16 @@
         <v>24</v>
       </c>
       <c r="B21" t="n">
-        <v>0.310545132764254</v>
+        <v>0.164389369040611</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0220575729373884</v>
+        <v>0.0221632719770524</v>
       </c>
       <c r="D21" t="n">
-        <v>14.0788441976709</v>
+        <v>7.41719765975068</v>
       </c>
       <c r="E21" t="n">
-        <v>0.00000000000000000000000000000000000000000000512409871043907</v>
+        <v>0.000000000000119624355573402</v>
       </c>
     </row>
     <row r="22">
@@ -806,16 +806,16 @@
         <v>25</v>
       </c>
       <c r="B22" t="n">
-        <v>0.0917326753013945</v>
+        <v>0.0428628624921881</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0116624975323777</v>
+        <v>0.0117626826817971</v>
       </c>
       <c r="D22" t="n">
-        <v>7.86561155076127</v>
+        <v>3.64396997281232</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0000000000000036729863721427</v>
+        <v>0.000268464754178944</v>
       </c>
     </row>
     <row r="23">
@@ -823,16 +823,16 @@
         <v>26</v>
       </c>
       <c r="B23" t="n">
-        <v>0.000218242899085799</v>
+        <v>0.000295258212902932</v>
       </c>
       <c r="C23" t="n">
-        <v>0.000038511955206292</v>
+        <v>0.0000385450204206041</v>
       </c>
       <c r="D23" t="n">
-        <v>5.66688702032306</v>
+        <v>7.66008707949998</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0000000145415154791241</v>
+        <v>0.0000000000000185807055724485</v>
       </c>
     </row>
     <row r="24">
@@ -840,13 +840,13 @@
         <v>27</v>
       </c>
       <c r="B24" t="n">
-        <v>0.121758440968355</v>
+        <v>0.113170422984952</v>
       </c>
       <c r="C24" t="n">
-        <v>0.000741149788926794</v>
+        <v>0.000681094769016513</v>
       </c>
       <c r="D24" t="n">
-        <v>164.283175665023</v>
+        <v>166.159583266757</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -857,13 +857,13 @@
         <v>28</v>
       </c>
       <c r="B25" t="n">
-        <v>0.265464198244439</v>
+        <v>0.276409031029294</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0016750021004017</v>
+        <v>0.00174201249254898</v>
       </c>
       <c r="D25" t="n">
-        <v>158.485889767407</v>
+        <v>158.672243862524</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>29</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.0712138961627018</v>
+        <v>-0.0702240349502626</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00126676168695663</v>
+        <v>0.00129294078783977</v>
       </c>
       <c r="D26" t="n">
-        <v>-56.2172797740604</v>
+        <v>-54.3134191532408</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
